--- a/artfynd/A 15947-2024 artfynd.xlsx
+++ b/artfynd/A 15947-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133369576</v>
+        <v>133369579</v>
       </c>
       <c r="B2" t="n">
-        <v>80473</v>
+        <v>96512</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>2667</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>350395</v>
+        <v>350362</v>
       </c>
       <c r="R2" t="n">
-        <v>6540993</v>
+        <v>6540930</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -775,7 +775,7 @@
         <v>133369577</v>
       </c>
       <c r="B3" t="n">
-        <v>96484</v>
+        <v>96501</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,50 +869,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133369578</v>
+        <v>133369580</v>
       </c>
       <c r="B4" t="n">
-        <v>8374</v>
+        <v>96261</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106540</v>
+        <v>2676</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Grov baronmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Anomodon viticulosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
+          <t>(Hedw.) Hook. &amp; Taylor</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Nagelhögen, Dls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>350395</v>
+        <v>350362</v>
       </c>
       <c r="R4" t="n">
-        <v>6540993</v>
+        <v>6540930</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -971,48 +966,51 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133369580</v>
+        <v>132061957</v>
       </c>
       <c r="B5" t="n">
-        <v>96244</v>
+        <v>80488</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2676</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grov baronmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Anomodon viticulosus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Hook. &amp; Taylor</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Nagelhögen, Dls</t>
+          <t>Nagelhögen S, Dls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>350362</v>
+        <v>350340</v>
       </c>
       <c r="R5" t="n">
-        <v>6540930</v>
+        <v>6540929</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1036,12 +1034,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På jätteek.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1050,50 +1053,51 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Anders Niklasson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Anders Niklasson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133369579</v>
+        <v>133369576</v>
       </c>
       <c r="B6" t="n">
-        <v>96495</v>
+        <v>80488</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2667</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1107,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>350362</v>
+        <v>350395</v>
       </c>
       <c r="R6" t="n">
-        <v>6540930</v>
+        <v>6540993</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1162,6 +1166,205 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>133369581</v>
+      </c>
+      <c r="B7" t="n">
+        <v>80488</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Nagelhögen, Dls</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>350343</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6540928</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Tisselskog</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>133369578</v>
+      </c>
+      <c r="B8" t="n">
+        <v>8374</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>106540</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Svart askbastborre</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hylesinus crenatus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Fabricius, 1787)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Nagelhögen, Dls</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>350395</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6540993</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Tisselskog</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 15947-2024 artfynd.xlsx
+++ b/artfynd/A 15947-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133369579</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133369577</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133369580</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1069,6 +1089,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132061957</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1166,6 +1191,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133369576</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1263,6 +1293,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133369581</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1365,8 +1400,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133369578</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>